--- a/Test_execution_summary.xlsx
+++ b/Test_execution_summary.xlsx
@@ -1420,10 +1420,10 @@
         <v>11</v>
       </c>
       <c r="B9" s="7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C9" s="7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D9" s="7">
         <v>1</v>
@@ -1454,10 +1454,10 @@
         <v>13</v>
       </c>
       <c r="B11" s="9">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C11" s="9">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D11" s="9">
         <v>5</v>
